--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486850_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486850_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.236700000000001</v>
+        <v>7.8629</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0126</v>
+        <v>5.7573</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2241</v>
+        <v>2.1056</v>
       </c>
       <c r="G2" t="n">
         <v>2.849</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7109</v>
+        <v>0.3371</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6114</v>
+        <v>0.3562</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0994</v>
+        <v>-0.0191</v>
       </c>
       <c r="V2" t="n">
         <v>2.8287</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9473</v>
+        <v>1.1252</v>
       </c>
       <c r="E3" t="n">
         <v>0.1822</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7652</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0.7276</v>
@@ -688,13 +688,13 @@
         <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0945</v>
+        <v>0.0834</v>
       </c>
       <c r="T3" t="n">
         <v>-0.2171</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1226</v>
+        <v>0.3005</v>
       </c>
       <c r="V3" t="n">
         <v>0.1088</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7536</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.616</v>
+        <v>0.1588</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1376</v>
+        <v>-0.0699</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1354</v>
@@ -766,13 +766,13 @@
         <v>0.4107</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1596</v>
+        <v>0.495</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8677</v>
+        <v>0.4106</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2919</v>
+        <v>0.0844</v>
       </c>
       <c r="V4" t="n">
         <v>-0.476</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0762</v>
+        <v>-0.1124</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.5316</v>
+        <v>-2.7796</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6079</v>
+        <v>2.6672</v>
       </c>
       <c r="G5" t="n">
         <v>0.8829</v>
@@ -844,13 +844,13 @@
         <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1077</v>
+        <v>-0.2963</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4066</v>
+        <v>0.1587</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5143</v>
+        <v>-0.455</v>
       </c>
       <c r="V5" t="n">
         <v>0.1224</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7954</v>
+        <v>-1.2287</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.4247</v>
+        <v>-4.0063</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6293</v>
+        <v>2.7775</v>
       </c>
       <c r="G6" t="n">
         <v>0.1635</v>
@@ -922,13 +922,13 @@
         <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0484</v>
+        <v>0.5182</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8486</v>
+        <v>-0.4302</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8002</v>
+        <v>0.9484</v>
       </c>
       <c r="V6" t="n">
         <v>1.1696</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>J. JUANOLA MADERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8058</v>
+        <v>-1.9842</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.235</v>
+        <v>-3.7465</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4292</v>
+        <v>1.7622</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9417</v>
+        <v>2.1781</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2233</v>
+        <v>2.5862</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2816</v>
+        <v>-0.4081</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5615</v>
+        <v>2.1002</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2852</v>
+        <v>3.0216</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2763</v>
+        <v>-0.9215</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6197</v>
+        <v>0.0779</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9382</v>
+        <v>-0.4355</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5579</v>
+        <v>0.5134</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2321</v>
+        <v>-3.9015</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2588</v>
+        <v>-5.5442</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6037</v>
+        <v>-0.0251</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4147</v>
+        <v>-0.3024</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0185</v>
+        <v>0.2773</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2357</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4166</v>
+        <v>-1.991</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1516</v>
+        <v>-4.0645</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.265</v>
+        <v>2.0735</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1295</v>
+        <v>-0.9417</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3666</v>
+        <v>-1.2233</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7629</v>
+        <v>0.2816</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1984</v>
+        <v>-1.5615</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3168</v>
+        <v>-0.2852</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1184</v>
+        <v>-1.2763</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0689</v>
+        <v>0.6197</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9502</v>
+        <v>-0.9382</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8813</v>
+        <v>1.5579</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0736</v>
+        <v>0.4185</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0386</v>
+        <v>-0.2443</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1122</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4189</v>
+        <v>-0.2357</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6591</v>
+        <v>-0.2357</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. JUANOLA MADERA</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0508</v>
+        <v>-2.4166</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.7538</v>
+        <v>-2.1516</v>
       </c>
       <c r="F9" t="n">
-        <v>1.703</v>
+        <v>-0.265</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1781</v>
+        <v>-1.1295</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5862</v>
+        <v>-0.3666</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4081</v>
+        <v>-0.7629</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1002</v>
+        <v>-1.1984</v>
       </c>
       <c r="K9" t="n">
-        <v>3.0216</v>
+        <v>-1.3168</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9215</v>
+        <v>0.1184</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0779</v>
+        <v>0.0689</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4355</v>
+        <v>0.9502</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5134</v>
+        <v>-0.8813</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.9015</v>
+        <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.5442</v>
+        <v>-1.2321</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0917</v>
+        <v>-0.0736</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3097</v>
+        <v>0.0386</v>
       </c>
       <c r="U9" t="n">
-        <v>0.218</v>
+        <v>-0.1122</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2357</v>
+        <v>-1.4189</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2357</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3892</v>
+        <v>-3.4586</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6146</v>
+        <v>-2.9212</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7746</v>
+        <v>-0.5374</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3303</v>
@@ -1234,13 +1234,13 @@
         <v>0.616</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4769</v>
+        <v>-0.5463</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6587</v>
+        <v>0.0348</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8182</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>1.0608</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.443999999999998</v>
+        <v>-2.114500000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.9005</v>
+        <v>-13.5714</v>
       </c>
       <c r="F11" t="n">
         <v>11.4567</v>
@@ -1279,7 +1279,7 @@
         <v>2.2642</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9883999999999993</v>
+        <v>0.9883999999999995</v>
       </c>
       <c r="I11" t="n">
         <v>1.2759</v>
@@ -1312,13 +1312,13 @@
         <v>11.2937</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5814000000000004</v>
+        <v>0.9108999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5245000000000005</v>
+        <v>-0.1951</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1059</v>
+        <v>1.106</v>
       </c>
       <c r="V11" t="n">
         <v>2.923999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.6987</v>
+        <v>6.7956</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8462</v>
+        <v>3.2186</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8525</v>
+        <v>3.577</v>
       </c>
       <c r="G12" t="n">
         <v>2.0382</v>
@@ -1390,13 +1390,13 @@
         <v>3.0801</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4901</v>
+        <v>0.587</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1586</v>
+        <v>-0.469</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3315</v>
+        <v>1.056</v>
       </c>
       <c r="V12" t="n">
         <v>2.117</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6153</v>
+        <v>4.3921</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0813</v>
+        <v>1.9767</v>
       </c>
       <c r="F13" t="n">
-        <v>2.534</v>
+        <v>2.4155</v>
       </c>
       <c r="G13" t="n">
         <v>3.0593</v>
@@ -1468,13 +1468,13 @@
         <v>1.8481</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9399</v>
+        <v>0.7168</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.6973</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1381</v>
+        <v>0.0195</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5793</v>
+        <v>0.8217</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0364</v>
+        <v>-1.0352</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6158</v>
+        <v>1.8569</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2408</v>
+        <v>0.6216</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1384</v>
+        <v>1.0899</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1023</v>
+        <v>-0.4682</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0056</v>
+        <v>0.0708</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7431</v>
+        <v>1.3076</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2625</v>
+        <v>-1.2368</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2351</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3953</v>
+        <v>-0.2177</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1602</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4107</v>
+        <v>2.4641</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6694</v>
+        <v>2.4641</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1065</v>
+        <v>0.0707</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2167</v>
+        <v>0.0501</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1102</v>
+        <v>0.0205</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.1786</v>
+        <v>-2.3347</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-1.1561</v>
       </c>
       <c r="X14" t="n">
         <v>-1.1786</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4469</v>
+        <v>0.5457</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.5582</v>
+        <v>0.3528</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0051</v>
+        <v>0.1929</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6216</v>
+        <v>1.1927</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0899</v>
+        <v>0.2272</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4682</v>
+        <v>0.9656</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0708</v>
+        <v>1.3951</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3076</v>
+        <v>0.1981</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2368</v>
+        <v>1.197</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5508999999999999</v>
+        <v>-0.2023</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2177</v>
+        <v>0.0291</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7685999999999999</v>
+        <v>-0.2314</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4641</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q15" t="n">
+        <v>-1.0267</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.2363</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.2208</v>
+      </c>
+      <c r="V15" t="n">
         <v>0</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.4641</v>
-      </c>
-      <c r="S15" t="n">
-        <v>-0.3042</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-0.4729</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.1687</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-2.3347</v>
-      </c>
       <c r="W15" t="n">
-        <v>-1.1561</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1133</v>
+        <v>0.4122</v>
       </c>
       <c r="E16" t="n">
-        <v>0.039</v>
+        <v>-1.7031</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0743</v>
+        <v>2.1153</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1927</v>
+        <v>-2.4637</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2272</v>
+        <v>-2.6664</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9656</v>
+        <v>0.2027</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3951</v>
+        <v>-2.5095</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1981</v>
+        <v>-2.3383</v>
       </c>
       <c r="L16" t="n">
-        <v>1.197</v>
+        <v>-0.1713</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2023</v>
+        <v>0.0458</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0291</v>
+        <v>-0.3281</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2314</v>
+        <v>0.374</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4107</v>
+        <v>1.6427</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R16" t="n">
-        <v>0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6687</v>
+        <v>-0.2945</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3294</v>
+        <v>-0.1668</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3394</v>
+        <v>-0.1277</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.5277</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1187</v>
+        <v>0.3265</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7186</v>
+        <v>-1.141</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5999</v>
+        <v>1.4675</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0397</v>
+        <v>1.2408</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7102000000000001</v>
+        <v>1.1384</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7498</v>
+        <v>0.1023</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3543</v>
+        <v>1.0056</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0122</v>
+        <v>0.7431</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6579</v>
+        <v>0.2625</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.394</v>
+        <v>0.2351</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.302</v>
+        <v>0.3953</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.092</v>
+        <v>-0.1602</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4107</v>
+        <v>0.4107</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>-2.2588</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6427</v>
+        <v>2.6694</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3316</v>
+        <v>-0.1463</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0195</v>
+        <v>0.1121</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3512</v>
+        <v>-0.2584</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3967</v>
+        <v>-0.3974</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0169</v>
+        <v>-2.5488</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6201</v>
+        <v>2.1514</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4637</v>
+        <v>-0.858</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.6664</v>
+        <v>0.5681</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2027</v>
+        <v>-1.4261</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.5095</v>
+        <v>-0.2356</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.3383</v>
+        <v>1.1461</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1713</v>
+        <v>-1.3817</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0458</v>
+        <v>-0.6224</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3281</v>
+        <v>-0.578</v>
       </c>
       <c r="O18" t="n">
-        <v>0.374</v>
+        <v>-0.0445</v>
       </c>
       <c r="P18" t="n">
         <v>1.6427</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8481</v>
+        <v>2.8748</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1035</v>
+        <v>-0.5928</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4806</v>
+        <v>-1.0812</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6229</v>
+        <v>0.4883</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5277</v>
+        <v>-0.5893</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3491</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0739</v>
+        <v>-0.4116</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9672</v>
+        <v>-2.0324</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8934</v>
+        <v>1.6208</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.858</v>
+        <v>-0.0397</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5681</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4261</v>
+        <v>-0.7498</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2356</v>
+        <v>0.3543</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1461</v>
+        <v>1.0122</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3817</v>
+        <v>-0.6579</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6224</v>
+        <v>-0.394</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.578</v>
+        <v>-0.302</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0445</v>
+        <v>-0.092</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.4107</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-2.0534</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.6427</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.2321</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.8748</v>
-      </c>
       <c r="S19" t="n">
-        <v>-1.2693</v>
+        <v>0.0387</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4996</v>
+        <v>-0.3333</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2303</v>
+        <v>0.3721</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8883</v>
+        <v>-2.5908</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8233</v>
+        <v>-2.5555</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.065</v>
+        <v>-0.0353</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9699</v>
@@ -2014,13 +2014,13 @@
         <v>0.4107</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9379</v>
+        <v>0.2353</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1971</v>
+        <v>0.4649</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2592</v>
+        <v>-0.2295</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2402</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.532</v>
+        <v>-6.7527</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.3026</v>
+        <v>-5.9888</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2294</v>
+        <v>-0.7639</v>
       </c>
       <c r="G21" t="n">
         <v>-5.0856</v>
@@ -2092,13 +2092,13 @@
         <v>2.0534</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0419</v>
+        <v>-0.2626</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6782</v>
+        <v>-0.3644</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3637</v>
+        <v>0.1019</v>
       </c>
       <c r="V21" t="n">
         <v>-2.2259</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.443899999999999</v>
+        <v>3.1413</v>
       </c>
       <c r="E22" t="n">
         <v>-11.4567</v>
       </c>
       <c r="F22" t="n">
-        <v>13.9007</v>
+        <v>14.5981</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2643</v>
@@ -2143,16 +2143,16 @@
         <v>-1.2759</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.0486</v>
+        <v>-2.048600000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6372000000000009</v>
+        <v>0.6372</v>
       </c>
       <c r="L22" t="n">
         <v>-2.6859</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2156</v>
+        <v>-0.2156000000000002</v>
       </c>
       <c r="N22" t="n">
         <v>-1.6256</v>
@@ -2170,13 +2170,13 @@
         <v>19.5074</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5816000000000003</v>
+        <v>0.1159999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>-1.1059</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5243999999999998</v>
+        <v>1.2219</v>
       </c>
       <c r="V22" t="n">
         <v>-2.924</v>
